--- a/Assets/Docments/Various Tables.xlsx
+++ b/Assets/Docments/Various Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\Space Combat\Assets\Docments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CA7D4B-7781-48F7-8501-5BDF52CDE73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10584BB9-7938-472F-A5AB-A032122BF6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AA13B329-E6C6-4D98-86A4-0B5567153B89}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA13B329-E6C6-4D98-86A4-0B5567153B89}"/>
   </bookViews>
   <sheets>
     <sheet name="Input Bindings" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Player Stats" sheetId="3" r:id="rId3"/>
     <sheet name="Weapons" sheetId="7" r:id="rId4"/>
     <sheet name="Obstacles-Resupply" sheetId="6" r:id="rId5"/>
+    <sheet name="Levels" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="184">
   <si>
     <t>Keyboard</t>
   </si>
@@ -141,9 +142,6 @@
     <t>Bomber/Kamikaze</t>
   </si>
   <si>
-    <t>Threat</t>
-  </si>
-  <si>
     <t>Capability</t>
   </si>
   <si>
@@ -153,15 +151,6 @@
     <t>No projectile weapons.  Self-destructs when getting close to the player.</t>
   </si>
   <si>
-    <t>They appear in straight lines and simple formations (e.g. V-shapes).  The threat is from their sheer number</t>
-  </si>
-  <si>
-    <t>The enter from the sides of the screen and used curved or diagonal paths to flank the player's position, forcing side-to-side movement.</t>
-  </si>
-  <si>
-    <t>They are generally slow but have high HP.  The force the player to prioritize targets and destroy them before they get too close.</t>
-  </si>
-  <si>
     <t>Sentinel/Shield Ship</t>
   </si>
   <si>
@@ -171,18 +160,12 @@
     <t>High HP, protected by a front-facing shield that deflects player shots.</t>
   </si>
   <si>
-    <t>Forces player to maneuver behind them or use special weapons.  Often appears in front of Grunts, acting as a screen.</t>
-  </si>
-  <si>
     <t>Spread Shooter</t>
   </si>
   <si>
     <t>Fires multiple, low-damage projectiles in a wide, fixed arc (e.g. 3 or 5-way shot.  Medium speed.</t>
   </si>
   <si>
-    <t>Creates "walls" of bullets that require precise micro-dodging within the gaps, covering a large area of the screen.</t>
-  </si>
-  <si>
     <t>Minelayer/Spawner</t>
   </si>
   <si>
@@ -198,30 +181,18 @@
     <t>Fires a slow homing missile or bullet with a slight turning radius.</t>
   </si>
   <si>
-    <t>Punishes slow or stationary play.  Forces the player to constantly be on the move and often lead the missile into an obstacle or another enemy.</t>
-  </si>
-  <si>
     <t>Pulsar/Ring Shooter</t>
   </si>
   <si>
     <t>Fires a dense ring of bullets, (omnidirectional), when it is destroyed or at set intervals.</t>
   </si>
   <si>
-    <t>Requires the player to calculate the exact timing or positioning to destroy it without being caught in the ensuing ring pattern.  High survivability.</t>
-  </si>
-  <si>
-    <t>Extremely difficult to target, breaks up attack patterns and forces the player to react instantly to its new location and fire.</t>
-  </si>
-  <si>
     <t>Dreadnought/Elite</t>
   </si>
   <si>
     <t>A mini-boss that appears multiple times during the level.  It combines the capabilities of two Tier 3 ships (e.g. Shielded Pulsar)</t>
   </si>
   <si>
-    <t>Acts as a major hurdle to the final boss.  Its destruction should be dramatic and high rewarding (e.g. a huge resource drop)</t>
-  </si>
-  <si>
     <t>Sovereign (Boss Battle)</t>
   </si>
   <si>
@@ -249,27 +220,12 @@
     <t>High speed.  Briefly cloaks and moves to a new, random, or pre-set position near the player every few seconds.</t>
   </si>
   <si>
-    <t>Spawn Weight</t>
-  </si>
-  <si>
-    <t>1 - 5</t>
-  </si>
-  <si>
-    <t>6 - 9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Large target with 2-3 main cannons firing slow, chunky bullets.  Simple circular movement pattern.</t>
   </si>
   <si>
-    <t>Introduces environmental clutter and forces the player to manage the battlefield as the hazards remain after the ship is destroyed.</t>
-  </si>
-  <si>
     <t>Can transition between a firing phase and a spawning phase, releasing waves of Minelayers, Predators, Pulsars, and Interceptors.</t>
   </si>
   <si>
@@ -318,15 +274,6 @@
     <t>Area of Effect, Homing, Max Damage</t>
   </si>
   <si>
-    <t>Level 1-5</t>
-  </si>
-  <si>
-    <t>Level 6-9</t>
-  </si>
-  <si>
-    <t>Level 10</t>
-  </si>
-  <si>
     <t>HP</t>
   </si>
   <si>
@@ -390,9 +337,6 @@
     <t>Add 20 points to armor - (up to Max)</t>
   </si>
   <si>
-    <t>Total Weight</t>
-  </si>
-  <si>
     <t>Mine Field</t>
   </si>
   <si>
@@ -565,6 +509,90 @@
   </si>
   <si>
     <t>Pulse Burst I</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>Star Base</t>
+  </si>
+  <si>
+    <t>1 - Green</t>
+  </si>
+  <si>
+    <t>3 - Yellow</t>
+  </si>
+  <si>
+    <t>5 - Red</t>
+  </si>
+  <si>
+    <t>4 - Orange</t>
+  </si>
+  <si>
+    <t>2 - Purple</t>
+  </si>
+  <si>
+    <t>.85</t>
+  </si>
+  <si>
+    <t>.65</t>
+  </si>
+  <si>
+    <t>.4</t>
+  </si>
+  <si>
+    <t>.15</t>
+  </si>
+  <si>
+    <t>.3</t>
+  </si>
+  <si>
+    <t>.05</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>.55</t>
+  </si>
+  <si>
+    <t>.7</t>
+  </si>
+  <si>
+    <t>.25</t>
+  </si>
+  <si>
+    <t>Enemies</t>
+  </si>
+  <si>
+    <t>Weight Level 2</t>
+  </si>
+  <si>
+    <t>Weight Level 3</t>
+  </si>
+  <si>
+    <t>Weight Level 4</t>
+  </si>
+  <si>
+    <t>Weight Level 5</t>
   </si>
 </sst>
 </file>
@@ -603,7 +631,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -652,11 +680,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -679,9 +716,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -694,6 +728,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -705,6 +758,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,77 +1222,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DF13FB-0913-458D-A7A4-20A664EC0491}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="18.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="6.7109375" style="7" customWidth="1"/>
-    <col min="3" max="4" width="26" style="6" customWidth="1"/>
-    <col min="5" max="6" width="6.5703125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8" style="7" customWidth="1"/>
-    <col min="10" max="10" width="7.5703125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="6" customWidth="1"/>
-    <col min="13" max="16384" width="18.28515625" style="6"/>
+    <col min="3" max="3" width="26" style="6" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="18.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="B1" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="D1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="16" t="s">
+      <c r="E1" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="G1" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="H1" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>30</v>
       </c>
@@ -1246,36 +1281,24 @@
       <c r="C3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="D3" s="9">
         <v>25</v>
       </c>
-      <c r="F3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9">
+        <v>10</v>
+      </c>
       <c r="G3" s="9">
         <v>10</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>10</v>
       </c>
-      <c r="I3" s="9">
-        <v>100</v>
-      </c>
-      <c r="J3" s="9">
-        <v>45</v>
-      </c>
-      <c r="K3" s="9">
-        <v>30</v>
-      </c>
-      <c r="L3" s="8">
-        <v>10</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="I3" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>31</v>
       </c>
@@ -1283,38 +1306,26 @@
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="9">
+        <v>34</v>
+      </c>
+      <c r="D4" s="9">
         <v>50</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9">
+        <v>15</v>
+      </c>
       <c r="G4" s="9">
         <v>15</v>
       </c>
-      <c r="H4" s="9">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9">
-        <v>50</v>
-      </c>
-      <c r="J4" s="9">
-        <v>60</v>
-      </c>
-      <c r="K4" s="9">
-        <v>50</v>
-      </c>
-      <c r="L4" s="8">
+      <c r="H4" s="8">
         <v>25</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="I4" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
@@ -1322,433 +1333,305 @@
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9">
+        <v>15</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9">
+        <v>40</v>
+      </c>
+      <c r="G5" s="9">
+        <v>90</v>
+      </c>
+      <c r="H5" s="8">
+        <v>100</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="9">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9">
-        <v>40</v>
-      </c>
-      <c r="H5" s="9">
-        <v>90</v>
-      </c>
-      <c r="I5" s="9">
-        <v>20</v>
-      </c>
-      <c r="J5" s="9">
-        <v>35</v>
-      </c>
-      <c r="K5" s="9">
-        <v>40</v>
-      </c>
-      <c r="L5" s="8">
-        <v>100</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="B6" s="9">
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="9">
+        <v>38</v>
+      </c>
+      <c r="D6" s="9">
         <v>20</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9">
+        <v>55</v>
+      </c>
       <c r="G6" s="9">
-        <v>55</v>
-      </c>
-      <c r="H6" s="9">
         <v>10</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="9">
-        <v>40</v>
-      </c>
-      <c r="K6" s="9">
-        <v>30</v>
-      </c>
-      <c r="L6" s="8">
+      <c r="H6" s="8">
         <v>200</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="I6" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B7" s="9">
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="9">
+        <v>40</v>
+      </c>
+      <c r="D7" s="9">
         <v>30</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9">
         <v>20</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="9">
-        <v>50</v>
-      </c>
-      <c r="K7" s="9">
-        <v>70</v>
-      </c>
-      <c r="L7" s="8">
+      <c r="G7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="8">
         <v>150</v>
       </c>
-      <c r="M7" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="I7" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" s="9">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9">
+        <v>60</v>
+      </c>
+      <c r="D8" s="9">
         <v>10</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9">
+        <v>70</v>
+      </c>
       <c r="G8" s="9">
-        <v>70</v>
-      </c>
-      <c r="H8" s="9">
         <v>25</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="8">
+      <c r="H8" s="8">
         <v>500</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="I8" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" s="9">
         <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="9">
+        <v>42</v>
+      </c>
+      <c r="D9" s="9">
         <v>40</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9">
         <v>35</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="9">
-        <v>25</v>
-      </c>
-      <c r="K9" s="9">
-        <v>35</v>
-      </c>
-      <c r="L9" s="8">
+      <c r="G9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="8">
         <v>300</v>
       </c>
-      <c r="M9" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="I9" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B10" s="9">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="9">
         <v>45</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9">
+      <c r="D10" s="9">
+        <v>45</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9">
         <v>30</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="9">
-        <v>40</v>
-      </c>
-      <c r="K10" s="9">
-        <v>45</v>
-      </c>
-      <c r="L10" s="8">
+      <c r="G10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="8">
         <v>400</v>
       </c>
-      <c r="M10" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="I10" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B11" s="9">
         <v>8</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="9">
+        <v>20</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9">
+        <v>50</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="9">
-        <v>20</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9">
-        <v>50</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="9">
-        <v>20</v>
-      </c>
-      <c r="K11" s="9">
-        <v>30</v>
-      </c>
-      <c r="L11" s="8">
+      <c r="H11" s="8">
         <v>500</v>
       </c>
-      <c r="M11" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="I11" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B12" s="9">
         <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="9">
+        <v>58</v>
+      </c>
+      <c r="D12" s="9">
         <v>75</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9">
+        <v>25</v>
+      </c>
       <c r="G12" s="9">
-        <v>25</v>
-      </c>
-      <c r="H12" s="9">
         <v>35</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J12" s="9">
-        <v>10</v>
-      </c>
-      <c r="K12" s="9">
-        <v>20</v>
-      </c>
-      <c r="L12" s="8">
+      <c r="H12" s="8">
         <v>750</v>
       </c>
-      <c r="M12" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="I12" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13" s="9">
         <v>9</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9">
+        <v>61</v>
+      </c>
+      <c r="D13" s="9">
         <v>15</v>
       </c>
-      <c r="F13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9">
+        <v>80</v>
+      </c>
       <c r="G13" s="9">
-        <v>80</v>
-      </c>
-      <c r="H13" s="9">
         <v>40</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L13" s="8">
+      <c r="H13" s="8">
         <v>7500</v>
       </c>
-      <c r="M13" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="I13" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B14" s="9">
         <v>10</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="9">
+        <v>49</v>
+      </c>
+      <c r="D14" s="9">
         <v>35</v>
       </c>
-      <c r="F14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9">
+        <v>85</v>
+      </c>
       <c r="G14" s="9">
-        <v>85</v>
-      </c>
-      <c r="H14" s="9">
         <v>55</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K14" s="9">
-        <v>5</v>
-      </c>
-      <c r="L14" s="8">
+      <c r="H14" s="8">
         <v>2500</v>
       </c>
-      <c r="M14" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="I14" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B15" s="9">
         <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9">
+        <v>51</v>
+      </c>
+      <c r="D15" s="9">
         <v>20</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9">
         <v>100</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L15" s="8">
+      <c r="G15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="8">
         <v>10000</v>
       </c>
-      <c r="M15" s="6" t="s">
-        <v>160</v>
+      <c r="I15" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="I1:K1"/>
+  <mergeCells count="8">
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1759,550 +1642,550 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="14" customWidth="1"/>
-    <col min="2" max="11" width="9" style="14" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="14"/>
+    <col min="1" max="1" width="23.42578125" style="13" customWidth="1"/>
+    <col min="2" max="11" width="9" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="11">
+    <row r="1" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="10">
         <v>1</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>2</v>
       </c>
-      <c r="D1" s="11">
+      <c r="D1" s="10">
         <v>3</v>
       </c>
-      <c r="E1" s="11">
+      <c r="E1" s="10">
         <v>4</v>
       </c>
-      <c r="F1" s="11">
+      <c r="F1" s="10">
         <v>5</v>
       </c>
-      <c r="G1" s="11">
+      <c r="G1" s="10">
         <v>6</v>
       </c>
-      <c r="H1" s="11">
+      <c r="H1" s="10">
         <v>7</v>
       </c>
-      <c r="I1" s="11">
+      <c r="I1" s="10">
         <v>8</v>
       </c>
-      <c r="J1" s="11">
+      <c r="J1" s="10">
         <v>9</v>
       </c>
-      <c r="K1" s="11">
+      <c r="K1" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="12">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <v>40</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>40</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>40</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>45</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>45</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>50</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <v>50</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <v>55</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <v>55</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="12">
         <v>150</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>155</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>160</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>160</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>165</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>165</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>170</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>170</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <v>175</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="12">
         <v>10</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <v>20</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>30</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>40</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>50</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>60</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>70</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>80</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>90</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>1</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>2</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>2</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>3</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>3</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>4</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>4</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <v>5</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="12">
         <v>50</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>55</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>60</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>65</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>70</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>75</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>80</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <v>85</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="12">
         <v>90</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="12">
         <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="12">
         <v>2</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>2</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>2</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>3</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>3</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>3</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>4</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <v>4</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <v>4</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="12">
         <v>0.5</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <v>0.5</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.45</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.45</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.4</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>0.4</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>0.35</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>0.3</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <v>0.25</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="13">
+      <c r="A10" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>0.6</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>0.6</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>0.65</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>0.65</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <v>0.7</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <v>0.7</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="12">
         <v>0.8</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="12">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="12">
         <v>20</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <v>20</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <v>25</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>25</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>30</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>30</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>35</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>40</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <v>45</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="13">
+      <c r="A12" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="12">
         <v>2</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
         <v>2</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>2</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>2</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>2</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>2</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <v>4</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <v>4</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <v>4</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="12">
         <v>1.5</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <v>1.5</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>1.25</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>1.25</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>1.1499999999999999</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>1</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>1</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <v>0.8</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="12">
         <v>0.75</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="12">
         <v>0.25</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="12">
         <v>0.25</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <v>0.35</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>0.35</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>0.5</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>0.5</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="12">
         <v>0.6</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="12">
         <v>0.65</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="12">
         <v>4</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="12">
         <v>4</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>5</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>5</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>6</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>6</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <v>7</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <v>8</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="12">
         <v>9</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="12">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="A16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="12">
         <v>1</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <v>1</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>1</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>1</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>3</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <v>3</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <v>3</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="12">
         <v>3</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2328,38 +2211,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="A1" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2367,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="C3" s="9">
         <v>80</v>
@@ -2380,7 +2263,7 @@
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2388,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C4" s="9">
         <v>80</v>
@@ -2401,7 +2284,7 @@
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2409,7 +2292,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C5" s="9">
         <v>90</v>
@@ -2422,7 +2305,7 @@
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2430,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C6" s="9">
         <v>80</v>
@@ -2443,7 +2326,7 @@
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2451,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="C7" s="9">
         <v>90</v>
@@ -2464,7 +2347,7 @@
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2472,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="C8" s="9">
         <v>80</v>
@@ -2485,7 +2368,7 @@
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2493,7 +2376,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C9" s="9">
         <v>90</v>
@@ -2506,7 +2389,7 @@
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2514,7 +2397,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C10" s="9">
         <v>80</v>
@@ -2527,7 +2410,7 @@
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2535,7 +2418,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C11" s="9">
         <v>90</v>
@@ -2548,7 +2431,7 @@
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2556,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C12" s="9">
         <v>100</v>
@@ -2569,43 +2452,43 @@
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:8" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="A14" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2613,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C16" s="9">
         <v>65</v>
@@ -2626,7 +2509,7 @@
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2634,7 +2517,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C17" s="9">
         <v>65</v>
@@ -2647,7 +2530,7 @@
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2655,7 +2538,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C18" s="9">
         <v>70</v>
@@ -2668,7 +2551,7 @@
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2676,7 +2559,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C19" s="9">
         <v>65</v>
@@ -2689,7 +2572,7 @@
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2697,7 +2580,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C20" s="9">
         <v>65</v>
@@ -2710,7 +2593,7 @@
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2718,7 +2601,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C21" s="9">
         <v>70</v>
@@ -2731,7 +2614,7 @@
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2739,7 +2622,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C22" s="9">
         <v>75</v>
@@ -2752,7 +2635,7 @@
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2760,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C23" s="9">
         <v>85</v>
@@ -2773,7 +2656,7 @@
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2781,7 +2664,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C24" s="9">
         <v>80</v>
@@ -2794,7 +2677,7 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2802,7 +2685,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C25" s="9">
         <v>90</v>
@@ -2815,7 +2698,7 @@
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2829,345 +2712,478 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4921E0-5401-4405-8667-712DBF5784AB}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="7" customWidth="1"/>
-    <col min="2" max="5" width="9.140625" style="7"/>
-    <col min="6" max="6" width="7.7109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="7"/>
+    <col min="2" max="2" width="9.140625" style="7"/>
+    <col min="3" max="7" width="7.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B2" s="9">
+        <v>20</v>
+      </c>
+      <c r="C2" s="9">
+        <v>5</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="9">
+        <v>50</v>
+      </c>
+      <c r="C3" s="9">
+        <v>150</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="9">
+        <v>5</v>
+      </c>
+      <c r="C4" s="9">
+        <v>10</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I8" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="B11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="9">
-        <v>40</v>
-      </c>
-      <c r="C2" s="9">
-        <v>40</v>
-      </c>
-      <c r="D2" s="9">
-        <v>40</v>
-      </c>
-      <c r="E2" s="9">
-        <v>20</v>
-      </c>
-      <c r="F2" s="9">
-        <v>5</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="B12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="9">
-        <v>10</v>
-      </c>
-      <c r="C3" s="9">
-        <v>10</v>
-      </c>
-      <c r="D3" s="9">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9">
-        <v>50</v>
-      </c>
-      <c r="F3" s="9">
-        <v>150</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="9">
-        <v>10</v>
-      </c>
-      <c r="C4" s="9">
-        <v>20</v>
-      </c>
-      <c r="D4" s="9">
-        <v>30</v>
-      </c>
-      <c r="E4" s="9">
-        <v>5</v>
-      </c>
-      <c r="F4" s="9">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="9">
-        <v>10</v>
-      </c>
-      <c r="C5" s="9">
-        <v>20</v>
-      </c>
-      <c r="D5" s="9">
-        <v>30</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="9">
-        <v>10</v>
-      </c>
-      <c r="C6" s="9">
-        <v>20</v>
-      </c>
-      <c r="D6" s="9">
-        <v>30</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="9">
-        <v>5</v>
-      </c>
-      <c r="C7" s="9">
-        <v>5</v>
-      </c>
-      <c r="D7" s="9">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="9">
-        <v>20</v>
-      </c>
-      <c r="C8" s="9">
-        <v>20</v>
-      </c>
-      <c r="D8" s="9">
-        <v>20</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="9">
-        <v>5</v>
-      </c>
-      <c r="C9" s="9">
-        <v>5</v>
-      </c>
-      <c r="D9" s="9">
-        <v>5</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" s="9">
-        <v>5</v>
-      </c>
-      <c r="C10" s="9">
-        <v>5</v>
-      </c>
-      <c r="D10" s="9">
-        <v>10</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="9">
-        <v>45</v>
-      </c>
-      <c r="C11" s="9">
-        <v>40</v>
-      </c>
-      <c r="D11" s="9">
-        <v>35</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="9">
-        <v>40</v>
-      </c>
-      <c r="C12" s="9">
-        <v>30</v>
-      </c>
-      <c r="D12" s="9">
-        <v>20</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="7">
-        <f>SUM(B2:B13)</f>
-        <v>200</v>
-      </c>
-      <c r="C14" s="7">
-        <f t="shared" ref="C14:D14" si="0">SUM(C2:C13)</f>
-        <v>215</v>
-      </c>
-      <c r="D14" s="7">
-        <f t="shared" si="0"/>
-        <v>235</v>
+      <c r="I12" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C7293A-143E-4431-A12E-1F42FA6D5925}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="6" style="18" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="14"/>
+    <col min="4" max="4" width="5.85546875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="14"/>
+    <col min="6" max="6" width="5.85546875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="14"/>
+    <col min="8" max="8" width="5.85546875" style="14" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" style="15"/>
+    <col min="11" max="19" width="6.42578125" style="15" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="16">
+        <v>0</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="20">
+        <f>B4*C4</f>
+        <v>85</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" s="20">
+        <f>$B4*E4</f>
+        <v>15</v>
+      </c>
+      <c r="G4" s="20">
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
+        <f t="shared" ref="H4:H7" si="0">$B4*G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="20">
+        <f t="shared" ref="D5:D7" si="1">B5*C5</f>
+        <v>97.5</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="20">
+        <f t="shared" ref="F5:F7" si="2">$B5*E5</f>
+        <v>45</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="20">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="20">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="20">
+        <f t="shared" si="2"/>
+        <v>110.00000000000001</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="20">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="20">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="20">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="20">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Docments/Various Tables.xlsx
+++ b/Assets/Docments/Various Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity\Space Combat\Assets\Docments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10584BB9-7938-472F-A5AB-A032122BF6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CEB534-2A0D-4643-A868-4F2D7B34C922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA13B329-E6C6-4D98-86A4-0B5567153B89}"/>
+    <workbookView xWindow="28740" yWindow="-16200" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{AA13B329-E6C6-4D98-86A4-0B5567153B89}"/>
   </bookViews>
   <sheets>
     <sheet name="Input Bindings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="187">
   <si>
     <t>Keyboard</t>
   </si>
@@ -493,9 +493,6 @@
     <t>3D Black Hole Shader</t>
   </si>
   <si>
-    <t>Breakable Asteroids</t>
-  </si>
-  <si>
     <t>Gas Cloud (VFX)</t>
   </si>
   <si>
@@ -593,6 +590,18 @@
   </si>
   <si>
     <t>Weight Level 5</t>
+  </si>
+  <si>
+    <t>Purple - Weight Level 2</t>
+  </si>
+  <si>
+    <t>Yellow - Weight Level 3</t>
+  </si>
+  <si>
+    <t>Orange - Weight Level 4</t>
+  </si>
+  <si>
+    <t>Red - Weight Level 5</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1693,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="12">
         <v>0</v>
@@ -2239,7 +2248,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>66</v>
@@ -2485,7 +2494,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>66</v>
@@ -2496,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="9">
         <v>65</v>
@@ -2712,7 +2721,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4921E0-5401-4405-8667-712DBF5784AB}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="7" customWidth="1"/>
@@ -2724,7 +2733,7 @@
     <col min="11" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>63</v>
       </c>
@@ -2735,22 +2744,22 @@
         <v>92</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>78</v>
       </c>
@@ -2770,11 +2779,8 @@
       <c r="I2" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>80</v>
       </c>
@@ -2795,7 +2801,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>98</v>
       </c>
@@ -2816,7 +2822,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>81</v>
       </c>
@@ -2837,7 +2843,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>83</v>
       </c>
@@ -2855,7 +2861,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>84</v>
       </c>
@@ -2876,7 +2882,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>87</v>
       </c>
@@ -2894,10 +2900,10 @@
         <v>93</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>88</v>
       </c>
@@ -2918,7 +2924,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>90</v>
       </c>
@@ -2936,48 +2942,74 @@
         <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I13" s="7" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9" t="s">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I14" s="7" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3006,7 +3038,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -3019,24 +3051,24 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="16">
@@ -3052,25 +3084,25 @@
       </c>
       <c r="H3" s="16"/>
       <c r="I3" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>164</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>165</v>
       </c>
       <c r="D4" s="20">
         <f>B4*C4</f>
         <v>85</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F4" s="20">
         <f>$B4*E4</f>
@@ -3086,27 +3118,27 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D5" s="20">
         <f t="shared" ref="D5:D7" si="1">B5*C5</f>
         <v>97.5</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F5" s="20">
         <f t="shared" ref="F5:F7" si="2">$B5*E5</f>
         <v>45</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
@@ -3115,27 +3147,27 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D6" s="20">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F6" s="20">
         <f t="shared" si="2"/>
         <v>110.00000000000001</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
@@ -3144,27 +3176,27 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D7" s="20">
         <f t="shared" si="1"/>
         <v>62.5</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F7" s="20">
         <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="0"/>
